--- a/客户通讯录_示例.xlsx
+++ b/客户通讯录_示例.xlsx
@@ -1,25 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x15ac">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\律师SaaS\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+  <x15ac:absPath url="G:\律师SaaS\"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="11655" windowHeight="9465"/>
+    <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="客户通讯录" sheetId="1" r:id="rId1"/>
+    <sheet name="客户通讯录" sheetId="1" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+  <si>
+    <t/>
+  </si>
   <si>
     <t>姓名</t>
   </si>
@@ -198,38 +196,65 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="300" formatCode="General"/>
+  </numFmts>
+  <fonts count="5">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <color rgb="FF175CEB"/>
+      <sz val="10"/>
+      <u/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Segoe UI Symbol"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
     <font>
-      <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -238,26 +263,27 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs>
+    <xf numFmtId="300" fontId="4" fillId="0" borderId="1" xfId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="300" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1"/>
+    <xf numFmtId="300" fontId="4" fillId="0" borderId="1" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -545,9 +571,10 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr/>
+  <dimension ref="G9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -558,201 +585,200 @@
     <col min="7" max="7" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:7">
+      <c r="A1" s="6">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="E1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="F1" s="4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A2" t="s">
+      <c r="G1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F2" t="s">
+      <c r="E2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G2" t="s">
+      <c r="F2" s="5" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A3" t="s">
+      <c r="G2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B3" t="s">
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D3" t="s">
+      <c r="C3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E3" t="s">
+      <c r="D3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F3" t="s">
+      <c r="E3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="G3" t="s">
+      <c r="F3" s="5" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A4" t="s">
+      <c r="G3" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B4" t="s">
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C4" t="s">
+      <c r="B4" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D4" t="s">
+      <c r="C4" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="F4" t="s">
+      <c r="D4" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G4" t="s">
+      <c r="F4" s="5" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A5" t="s">
+      <c r="G4" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B5" t="s">
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D5" t="s">
+      <c r="B5" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E5" t="s">
+      <c r="D5" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="F5" t="s">
+      <c r="E5" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G5" t="s">
+      <c r="F5" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A6" t="s">
+      <c r="G5" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B6" t="s">
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C6" t="s">
+      <c r="B6" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D6" t="s">
+      <c r="C6" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="E6" t="s">
+      <c r="D6" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="F6" t="s">
+      <c r="E6" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="G6" t="s">
+      <c r="F6" s="5" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A7" t="s">
+      <c r="G6" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B7" t="s">
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C7" t="s">
+      <c r="B7" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="E7" t="s">
+      <c r="C7" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="F7" t="s">
+      <c r="E7" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="G7" t="s">
+      <c r="F7" s="5" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A8" t="s">
+      <c r="G7" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B8" t="s">
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D8" t="s">
+      <c r="B8" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="F8" t="s">
+      <c r="D8" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="G8" t="s">
+      <c r="F8" s="5" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A9" t="s">
+      <c r="G8" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B9" t="s">
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C9" t="s">
+      <c r="B9" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="D9" t="s">
+      <c r="C9" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E9" t="s">
+      <c r="D9" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="F9" t="s">
+      <c r="E9" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="G9" t="s">
+      <c r="F9" s="5" t="s">
         <v>57</v>
       </c>
+      <c r="G9" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>